--- a/education_forms/043_primary_school_parent_payments_online_form--education_forms.xlsx
+++ b/education_forms/043_primary_school_parent_payments_online_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>payment_details</t>
+          <t>What is the payment method and amount?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Select payment method</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one or more methods</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +575,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>payment_date</t>
+          <t>Enter payment date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +598,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>Enter payment amount</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +621,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>payment_reference</t>
+          <t>Enter payment reference</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +644,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>Student School ID</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +667,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>Student ID</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +690,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>payment_status</t>
+          <t>Payment Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,36 +713,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>payment_amount</t>
+          <t>Payment Amount</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>parent_name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>Parent Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,41 +754,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>payment_date</t>
+          <t>payment_date_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>payment_date</t>
+          <t>Payment Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>payment_method_confirmation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>school_id</t>
+          <t>Confirm payment method</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,12 +803,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +836,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -849,29 +853,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -883,44 +887,61 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_confirmation_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>payment_method_confirmation_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
